--- a/data_out/country_spreadsheets/Spain.xlsx
+++ b/data_out/country_spreadsheets/Spain.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W60"/>
+  <dimension ref="A1:AN60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>65.47</v>
       </c>
+      <c r="X2" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>154.18</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>104.89</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>57.12</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>249.43</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>101.54</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>77</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>83.20999999999999</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>67.09</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>65.47</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>73.68000000000001</v>
       </c>
+      <c r="X3" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>248.88</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>166.58</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>50.53</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>256.08</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>66.18000000000001</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>112.47</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>65.59</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>73.68000000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>76.67</v>
       </c>
+      <c r="X4" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>187.47</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>136.6</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>63.67</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>278.61</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>41.73</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>235.41</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>39.87</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>76.67</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>89.11</v>
       </c>
+      <c r="X5" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>84.92</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>120.41</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>70.01000000000001</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>229.6</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>103.37</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>66.01000000000001</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>22.78</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>133.62</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>64.28</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>89.11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>143.04</v>
       </c>
+      <c r="X6" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>34.38</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>175.46</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>87.41</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>83.89</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>214.4</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10.42</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>169.93</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>66.36</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>135.42</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>160.29</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>143.04</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>31.42</v>
       </c>
+      <c r="X7" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>90.87</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>84.48</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>116.57</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>159.92</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>124.16</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>30.31</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>31.42</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>37.66</v>
       </c>
+      <c r="X8" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>186.82</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>97.31999999999999</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>174.85</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>172.93</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>142.41</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>37.66</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>36.32</v>
       </c>
+      <c r="X9" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>33.54</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>61.34</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>109.27</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>30.91</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>136.95</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>85.23</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>36.32</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>6.71</v>
       </c>
+      <c r="X10" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>43.87</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>57.49</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>30.89</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>6.71</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>20.67</v>
       </c>
+      <c r="X11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>177.73</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>52.87</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>66.48999999999999</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>154.7</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>102.65</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20.67</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>14.28</v>
       </c>
+      <c r="X12" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>73.31</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>230.71</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>53.11</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>149.28</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>38.05</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>58.88</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>139.98</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>133.48</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>14.28</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>4.08</v>
       </c>
+      <c r="X13" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>177.23</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>15.48</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>33.04</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>48.95</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>46.15</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>105.31</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>53.55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>4.08</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>4.88</v>
       </c>
+      <c r="X14" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>189.76</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>20.04</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>101.42</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>163.93</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>174.1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>155.65</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>33.68</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>109.22</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>167.88</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>4.88</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1622,6 +2370,57 @@
       <c r="W15" t="n">
         <v>2.21</v>
       </c>
+      <c r="X15" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>80.67</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>205.02</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>72.48999999999999</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>53.31</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.21</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1699,6 +2498,57 @@
       <c r="W16" t="n">
         <v>42.3</v>
       </c>
+      <c r="X16" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>226.34</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>98.51000000000001</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>76.27</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>118.53</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>82.84999999999999</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>105.98</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>53.77</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>217.12</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>50.08</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>125.68</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>42.3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1776,6 +2626,57 @@
       <c r="W17" t="n">
         <v>53.2</v>
       </c>
+      <c r="X17" t="n">
+        <v>13.08</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>53.12</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>282.94</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>70.36</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>133.31</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>100.04</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>213.67</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>102.28</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>53.2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1853,6 +2754,57 @@
       <c r="W18" t="n">
         <v>22.73</v>
       </c>
+      <c r="X18" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>199.74</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>50.66</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>254.83</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>63.71</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>88.16</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>32.49</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>217.47</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>116.63</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>22.73</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1930,6 +2882,57 @@
       <c r="W19" t="n">
         <v>75.51000000000001</v>
       </c>
+      <c r="X19" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>58.37</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>252.99</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>30.66</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>106.66</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>270.66</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>71.66</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>132.67</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>38.12</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>184.28</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>75.51000000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2007,6 +3010,57 @@
       <c r="W20" t="n">
         <v>41.82</v>
       </c>
+      <c r="X20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>70.48</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>252.08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>44.86</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>333.27</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>126.29</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>146.07</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>35.55</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>188.84</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>41.82</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2084,6 +3138,57 @@
       <c r="W21" t="n">
         <v>37.46</v>
       </c>
+      <c r="X21" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>79.88</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>264.26</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>149.47</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>207.31</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>93.36</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>110.48</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>168.76</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>37.46</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2161,6 +3266,57 @@
       <c r="W22" t="n">
         <v>49.14</v>
       </c>
+      <c r="X22" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>244.3</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>34.08</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>22.26</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>156.62</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>140.22</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>181.43</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>94.01000000000001</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>49.14</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2238,6 +3394,57 @@
       <c r="W23" t="n">
         <v>1.89</v>
       </c>
+      <c r="X23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>265.65</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>11.41</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>120.37</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>48.04</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>145.39</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>67.56</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.89</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2315,6 +3522,57 @@
       <c r="W24" t="n">
         <v>34.1</v>
       </c>
+      <c r="X24" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2017</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>293.32</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>269.73</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>115.23</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>207.98</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>16.55</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>190.45</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>84.87</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>15.14</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>34.1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2392,6 +3650,57 @@
       <c r="W25" t="n">
         <v>72.90000000000001</v>
       </c>
+      <c r="X25" t="n">
+        <v>13.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>93.59</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>290.24</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>90.88</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>239.93</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>147.13</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>223.57</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>68.16</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>271.86</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>53.16</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>72.90000000000001</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2469,6 +3778,57 @@
       <c r="W26" t="n">
         <v>67.56</v>
       </c>
+      <c r="X26" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>250.2</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>147.11</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>82.11</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>204.13</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>84.69</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>80.19</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>120.24</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>110.93</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>67.56</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2546,6 +3906,57 @@
       <c r="W27" t="n">
         <v>24.1</v>
       </c>
+      <c r="X27" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>61.61</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>221.89</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>17.53</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>94.42</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>174.14</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>151.17</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>61.28</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>137.43</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>36.99</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>24.1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2623,6 +4034,57 @@
       <c r="W28" t="n">
         <v>33.25</v>
       </c>
+      <c r="X28" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>28.43</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>159.92</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>27.23</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>119.51</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>207.86</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>75.81</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>81.22</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>169.76</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>126.25</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>33.25</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2700,6 +4162,57 @@
       <c r="W29" t="n">
         <v>15.19</v>
       </c>
+      <c r="X29" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>46.53</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>248.02</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>83.38</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>107.66</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>91.56</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>68.98</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>138.77</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>59.76</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>57.82</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>97.48</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>15.19</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2777,6 +4290,57 @@
       <c r="W30" t="n">
         <v>21.57</v>
       </c>
+      <c r="X30" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>61.29</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>229.92</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>78.34999999999999</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>99.73</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>161.02</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>63.95</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>215.73</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>105.34</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>84.05</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>111.28</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>90.36</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>21.57</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2854,6 +4418,57 @@
       <c r="W31" t="n">
         <v>40.1</v>
       </c>
+      <c r="X31" t="n">
+        <v>18.82</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>87.31999999999999</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>236.79</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>150.34</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>68.65000000000001</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>244.47</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>44.61</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>168.08</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>128.34</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>40.1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2931,6 +4546,57 @@
       <c r="W32" t="n">
         <v>58.02</v>
       </c>
+      <c r="X32" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>93.58</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>235.16</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>118.24</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>141.25</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>174.86</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>122.94</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>39.01</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>58.02</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -3008,6 +4674,57 @@
       <c r="W33" t="n">
         <v>1.46</v>
       </c>
+      <c r="X33" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>57.08</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>167.85</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>130.22</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>33.49</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>102.13</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>217.75</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>125.01</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.46</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -3085,6 +4802,57 @@
       <c r="W34" t="n">
         <v>2.16</v>
       </c>
+      <c r="X34" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>114.73</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>141.84</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>76.65000000000001</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>58.24</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>27.19</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>73.53</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>167.33</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>116.38</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>2.16</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -3162,6 +4930,57 @@
       <c r="W35" t="n">
         <v>8.94</v>
       </c>
+      <c r="X35" t="n">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>146.31</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>26.06</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>53.19</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>167.48</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>151.27</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>103.86</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>8.94</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -3239,6 +5058,57 @@
       <c r="W36" t="n">
         <v>11.95</v>
       </c>
+      <c r="X36" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>79.02</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>169.9</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>34.32</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>240.79</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>159.43</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>142.88</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>34.35</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>58.98</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>207.23</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>170.84</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>11.95</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -3316,6 +5186,57 @@
       <c r="W37" t="n">
         <v>140.34</v>
       </c>
+      <c r="X37" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>118.77</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>110.97</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>249.36</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>251.06</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>227.67</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>23.54</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>20.76</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>287.31</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>140.34</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -3393,6 +5314,57 @@
       <c r="W38" t="n">
         <v>2.46</v>
       </c>
+      <c r="X38" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>56.02</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>164.36</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>234.87</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>28.07</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>181.07</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>103.21</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>209.53</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>116.77</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>227.13</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>2.46</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -3470,6 +5442,57 @@
       <c r="W39" t="n">
         <v>4.07</v>
       </c>
+      <c r="X39" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>88.78</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2014</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>220.37</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>273.2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>247.97</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>34.33</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>119.29</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>194.25</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>4.07</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -3547,6 +5570,57 @@
       <c r="W40" t="n">
         <v>15.54</v>
       </c>
+      <c r="X40" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>95.11</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>233.44</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>151.23</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>97.25</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>39.88</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>150.14</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>15.54</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -3624,6 +5698,57 @@
       <c r="W41" t="n">
         <v>18.19</v>
       </c>
+      <c r="X41" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>105.02</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>158.21</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>101.14</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>44.27</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>60.57</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>161.33</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>18.19</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -3701,6 +5826,57 @@
       <c r="W42" t="n">
         <v>42.67</v>
       </c>
+      <c r="X42" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>67.43000000000001</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>144.52</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>39.91</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>327</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>136.89</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>41.97</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>49.97</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>28.38</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>85.58</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>189.81</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>42.67</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -3778,6 +5954,57 @@
       <c r="W43" t="n">
         <v>175.01</v>
       </c>
+      <c r="X43" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>104.49</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2016</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>164.02</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>259.39</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>167.06</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>307.81</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>183.41</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>55.73</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>107.48</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>142.55</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>158.77</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>288.92</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>175.01</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -3855,6 +6082,57 @@
       <c r="W44" t="n">
         <v>28.9</v>
       </c>
+      <c r="X44" t="n">
+        <v>12.37</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>127</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>25.61</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>68.48</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>63.42</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>104.47</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>101.52</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>136.27</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>82.98</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>28.9</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -3932,6 +6210,57 @@
       <c r="W45" t="n">
         <v>26.07</v>
       </c>
+      <c r="X45" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>101.24</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>252.53</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>42.26</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>66.31</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>108.76</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>53.87</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>172.53</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>35.13</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>92.08</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>155.54</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>99.58</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>40.98</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>26.07</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -4009,6 +6338,57 @@
       <c r="W46" t="n">
         <v>98.87</v>
       </c>
+      <c r="X46" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>68.59</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>145.99</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>58.75</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>211.88</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>152.48</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>77.84999999999999</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>134.09</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>34.15</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>129.09</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>210.66</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>169.44</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>165</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>98.87</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -4086,6 +6466,57 @@
       <c r="W47" t="n">
         <v>12.84</v>
       </c>
+      <c r="X47" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>106.39</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>244.56</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>22.05</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>49.88</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>74.31999999999999</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>19.66</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>167.4</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>62.69</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>118.22</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>90.23999999999999</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>12.84</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -4163,6 +6594,57 @@
       <c r="W48" t="n">
         <v>61.2</v>
       </c>
+      <c r="X48" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>79.23999999999999</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>199.38</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>29.13</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>36.78</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>148.13</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>122.68</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>159.82</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>62.41</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>137.45</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>71.47</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>61.2</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -4240,6 +6722,57 @@
       <c r="W49" t="n">
         <v>29.54</v>
       </c>
+      <c r="X49" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>83.42</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>115.74</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>144.46</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>70.72</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>73.44</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>156.35</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>243.29</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>219.97</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>29.54</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -4317,6 +6850,57 @@
       <c r="W50" t="n">
         <v>9.85</v>
       </c>
+      <c r="X50" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>99.94</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>237.9</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>63.4</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>80.31</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>55.74</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>142.73</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>146.37</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>9.85</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -4394,6 +6978,57 @@
       <c r="W51" t="n">
         <v>111.56</v>
       </c>
+      <c r="X51" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>152.34</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>37.45</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>316.36</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>211.98</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>297.99</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>138.16</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>38.03</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>104.75</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>73.93000000000001</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>151.95</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>306.94</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>111.56</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -4471,6 +7106,57 @@
       <c r="W52" t="n">
         <v>0.28</v>
       </c>
+      <c r="X52" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0.28</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -4548,6 +7234,57 @@
       <c r="W53" t="n">
         <v>75.06999999999999</v>
       </c>
+      <c r="X53" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>99.13</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>205.33</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>12.41</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>156.83</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>191.54</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>119.25</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>125.45</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>188.84</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>78.58</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>75.06999999999999</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -4625,6 +7362,57 @@
       <c r="W54" t="n">
         <v>35.46</v>
       </c>
+      <c r="X54" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>81.23999999999999</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>82.55</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>70.26000000000001</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>83.04000000000001</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>28.42</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>35.46</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -4702,6 +7490,57 @@
       <c r="W55" t="n">
         <v>13.4</v>
       </c>
+      <c r="X55" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>19.82</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>13.4</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -4779,6 +7618,57 @@
       <c r="W56" t="n">
         <v>56.76</v>
       </c>
+      <c r="X56" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>106.07</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>108.01</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>35.38</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>84.20999999999999</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>67.78</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>56.76</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -4856,6 +7746,57 @@
       <c r="W57" t="n">
         <v>11.74</v>
       </c>
+      <c r="X57" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>149.48</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>94.52</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>98.62</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>110.81</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>115.16</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>11.69</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>11.74</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -4933,6 +7874,57 @@
       <c r="W58" t="n">
         <v>13.36</v>
       </c>
+      <c r="X58" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>176.34</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>75.42</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>173.23</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>127.43</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>74.89</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>115.05</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>166.48</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>76.73999999999999</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>13.36</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -5010,6 +8002,57 @@
       <c r="W59" t="n">
         <v>13.07</v>
       </c>
+      <c r="X59" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>25.68</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>24.54</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>18.35</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>27.01</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>13.07</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -5085,6 +8128,57 @@
         <v>140.77</v>
       </c>
       <c r="W60" t="n">
+        <v>113.37</v>
+      </c>
+      <c r="X60" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>2012</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>91.69</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>148.89</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>64.47</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>94.27</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>135.54</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>140.77</v>
+      </c>
+      <c r="AN60" t="n">
         <v>113.37</v>
       </c>
     </row>
